--- a/SampleFiles/Directory Of Files/File 03.xlsx
+++ b/SampleFiles/Directory Of Files/File 03.xlsx
@@ -8,10 +8,11 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Budget" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Staffing" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" name="B" vbProcedure="false">Sheet1!$A$11</definedName>
+    <definedName function="false" hidden="false" name="B" vbProcedure="false">Budget!$A$11</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,26 +24,149 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
-  <si>
-    <t xml:space="preserve">F16 Text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B17 Text</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="42">
+  <si>
+    <t xml:space="preserve">My Organization Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Department Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Department Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salaries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travel Costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supplies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Office Supplies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staffing Sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employee Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employee Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rate/ Hr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yearly Hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benefits Factor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benefits Cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual Cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marcus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thorne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logistics &amp; Supply Chain Coordinator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saanvi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reddy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Industrial Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Julian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quality Assurance (QA) Inspector</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Okafor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isabel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duarte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naomi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sterling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tanaka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="[$$-1009]#,##0.00;[RED]\-[$$-1009]#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -59,20 +183,54 @@
       <name val="Arial"/>
       <family val="0"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor rgb="FFCCCCFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
@@ -102,8 +260,44 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -116,6 +310,66 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFCCCCCC"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -232,31 +486,106 @@
   </sheetPr>
   <dimension ref="A1:F32"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20.35"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E1" s="0" t="n">
-        <v>10</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="str">
+        <f aca="false">"Department "&amp;B2</f>
+        <v>Department 1234</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <f aca="false">Staffing!H16</f>
+        <v>788182.25</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>5571</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>5572</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>5573</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>5574</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>1500</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
-        <v>10</v>
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <f aca="false">SUM(C5:C9)</f>
+        <v>814682.25</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F16" s="0" t="s">
-        <v>0</v>
-      </c>
+      <c r="F16" s="1"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="0" t="s">
-        <v>1</v>
-      </c>
+      <c r="B17" s="1"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C32" s="0" t="n">
-        <v>18</v>
-      </c>
+      <c r="C32" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -267,4 +596,368 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="38.67"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="4" style="4" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13.22"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>1920</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <f aca="false">D6*E6*F6</f>
+        <v>9696</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <f aca="false">D6*E6+G6</f>
+        <v>58176</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>40.25</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>1920</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <f aca="false">D7*E7*F7</f>
+        <v>23184</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <f aca="false">D7*E7+G7</f>
+        <v>100464</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>1920</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <f aca="false">D8*E8*F8</f>
+        <v>41760</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <f aca="false">D8*E8+G8</f>
+        <v>180960</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>1920</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <f aca="false">D9*E9*F9</f>
+        <v>17472</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <f aca="false">D9*E9+G9</f>
+        <v>104832</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>1920</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <f aca="false">D10*E10*F10</f>
+        <v>9696</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <f aca="false">D10*E10+G10</f>
+        <v>58176</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <f aca="false">D11*E11*F11</f>
+        <v>9405</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <f aca="false">D11*E11+G11</f>
+        <v>56430</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>1700</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <f aca="false">D12*E12*F12</f>
+        <v>10455</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <f aca="false">D12*E12+G12</f>
+        <v>62730</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <f aca="false">D13*E13*F13</f>
+        <v>8332.5</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <f aca="false">D13*E13+G13</f>
+        <v>49995</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>40.25</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>970</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <f aca="false">D14*E14*F14</f>
+        <v>11712.75</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <f aca="false">D14*E14+G14</f>
+        <v>50755.25</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>1920</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <f aca="false">D15*E15*F15</f>
+        <v>10944</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <f aca="false">D15*E15+G15</f>
+        <v>65664</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="9"/>
+      <c r="E16" s="8" t="n">
+        <f aca="false">SUM(E6:E15)</f>
+        <v>17490</v>
+      </c>
+      <c r="F16" s="8"/>
+      <c r="G16" s="9" t="n">
+        <f aca="false">SUM(G6:G15)</f>
+        <v>152657.25</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <f aca="false">SUM(H6:H15)</f>
+        <v>788182.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>